--- a/public/data/xlsx/etl4.xlsx
+++ b/public/data/xlsx/etl4.xlsx
@@ -428,6 +428,18 @@
   </sheetPr>
   <dimension ref="A1:J790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -24957,6 +24969,11 @@
   </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -25108,6 +25125,12 @@
   </sheetPr>
   <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -26848,6 +26871,11 @@
   </sheetPr>
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -27035,6 +27063,10 @@
   </sheetPr>
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -27141,6 +27173,25 @@
   </sheetPr>
   <dimension ref="A1:Q790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
